--- a/test/fixtures/xlsx/layout-edge/layout-edge.xlsx
+++ b/test/fixtures/xlsx/layout-edge/layout-edge.xlsx
@@ -12,63 +12,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
-  <si>
-    <t xml:space="preserve">~~table:OffsetTable~~</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+  <si>
+    <t xml:space="preserve">:table OffsetTable</t>
   </si>
   <si>
     <t xml:space="preserve">Starts at F9 rather than the top-left corner.</t>
   </si>
   <si>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
     <t xml:space="preserve">index</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
+    <t xml:space="preserve">cs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">cs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~~table:SecondTable~~</t>
+    <t xml:space="preserve">:table SecondTable</t>
   </si>
   <si>
     <t xml:space="preserve">Keeps the ragged row from being trimmed as a trailing blank.</t>
@@ -134,181 +146,179 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A9:H28"/>
+  <dimension ref="A9:I24"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="9">
       <c r="F9" t="s">
         <v>0</v>
       </c>
+      <c r="G9" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="F10" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="F11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" t="s">
         <v>7</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="I11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="F12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" t="s">
         <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="I12" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="F13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" t="s">
         <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="I13" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="14">
-      <c r="F14" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15">
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
         <v>6</v>
       </c>
-      <c r="G15" t="s">
-        <v>6</v>
-      </c>
-      <c r="H15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" t="s">
-        <v>5</v>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="F21" t="s">
-        <v>18</v>
+        <v>3</v>
+      </c>
+      <c r="G21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>19</v>
+        <v>4</v>
+      </c>
+      <c r="G22" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H23" t="s">
-        <v>22</v>
+        <v>9</v>
+      </c>
+      <c r="I23" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="24">
-      <c r="F24" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="F25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="F26" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" t="s">
-        <v>5</v>
-      </c>
-      <c r="H26" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="F27" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" t="s">
-        <v>6</v>
-      </c>
-      <c r="H27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="I24" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
